--- a/artfynd/A 60387-2023 artfynd.xlsx
+++ b/artfynd/A 60387-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60387-2023 artfynd.xlsx
+++ b/artfynd/A 60387-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114397180</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,7 +716,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öraderyd (Öraderyd), Hl</t>
+          <t>Öraderyd, Öraderyd, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 60387-2023 artfynd.xlsx
+++ b/artfynd/A 60387-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114397180</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60387-2023 artfynd.xlsx
+++ b/artfynd/A 60387-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114397180</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60387-2023 artfynd.xlsx
+++ b/artfynd/A 60387-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114397180</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
